--- a/kinase_project-final-tables.xlsx
+++ b/kinase_project-final-tables.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10525"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10917"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/granepura/Graduate Center Dropbox/Gehan Ranepura/mcce-development-2024/Kinase_Project/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3F6C24AB-6869-0D45-BBCD-C238D84021CD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{825F7430-D224-864E-AD1F-786D52C3E864}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1640" yWindow="660" windowWidth="30240" windowHeight="17920" activeTab="4" xr2:uid="{37B80709-00A1-9846-BFB3-D09BF45DC0B4}"/>
+    <workbookView xWindow="0" yWindow="660" windowWidth="30240" windowHeight="17920" activeTab="5" xr2:uid="{37B80709-00A1-9846-BFB3-D09BF45DC0B4}"/>
   </bookViews>
   <sheets>
     <sheet name="PWD" sheetId="2" r:id="rId1"/>
@@ -41,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1461" uniqueCount="433">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1461" uniqueCount="435">
   <si>
     <t>Info regarding runs</t>
   </si>
@@ -1340,6 +1340,12 @@
   </si>
   <si>
     <t>4AGD/xts_sum_crg.out:Net_Charge</t>
+  </si>
+  <si>
+    <t>N13, N21, N48, N3</t>
+  </si>
+  <si>
+    <t>N82, N15, N3</t>
   </si>
 </sst>
 </file>
@@ -1351,7 +1357,7 @@
     <numFmt numFmtId="165" formatCode="0.000"/>
     <numFmt numFmtId="166" formatCode="#,##0.0"/>
   </numFmts>
-  <fonts count="21" x14ac:knownFonts="1">
+  <fonts count="20" x14ac:knownFonts="1">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -1482,14 +1488,6 @@
       <name val="Aptos Narrow"/>
       <family val="2"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <i/>
-      <sz val="12"/>
-      <color rgb="FF000000"/>
-      <name val="Arial"/>
-      <family val="2"/>
     </font>
     <font>
       <b/>
@@ -1849,7 +1847,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="304">
+  <cellXfs count="279">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="4" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
@@ -2367,60 +2365,6 @@
     <xf numFmtId="4" fontId="15" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="2" fontId="9" fillId="0" borderId="18" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="2" fontId="9" fillId="0" borderId="21" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="13" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="12" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="15" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="2" fontId="9" fillId="3" borderId="19" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="3" borderId="25" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="3" borderId="26" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="3" borderId="24" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="2" fontId="10" fillId="0" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="2" fontId="10" fillId="0" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="2" fontId="10" fillId="0" borderId="15" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="2" fontId="10" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="2" fontId="10" fillId="0" borderId="18" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="165" fontId="10" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -2440,15 +2384,6 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="165" fontId="10" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="2" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -2471,13 +2406,10 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="10" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="4" fontId="19" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="165" fontId="5" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -2490,39 +2422,6 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="165" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="4" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="3" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="2" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="2" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="4" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="9" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="2" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="4" fontId="3" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="165" fontId="2" fillId="3" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -2562,19 +2461,13 @@
     <xf numFmtId="2" fontId="1" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="2" fontId="2" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="2" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="2" fontId="5" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -2620,17 +2513,8 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="3" fontId="3" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="4" fontId="2" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="2" fontId="3" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="4" fontId="2" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="4" fontId="3" fillId="3" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -2647,41 +2531,86 @@
     <xf numFmtId="0" fontId="2" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="26" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="9" fillId="0" borderId="18" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="2" fontId="9" fillId="0" borderId="21" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="13" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="12" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="15" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="9" fillId="3" borderId="19" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="25" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="26" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="24" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="10" fillId="0" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="2" fontId="10" fillId="0" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="2" fontId="10" fillId="0" borderId="15" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="10" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="10" fillId="0" borderId="18" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
@@ -2690,67 +2619,6 @@
     <cellStyle name="Normal 2" xfId="1" xr:uid="{299B3A41-EA04-A748-A902-612F2A01A105}"/>
   </cellStyles>
   <dxfs count="57">
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="5"/>
-        </patternFill>
-      </fill>
-      <border>
-        <left/>
-        <right/>
-        <top/>
-        <bottom/>
-      </border>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="5" tint="0.59996337778862885"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="0"/>
-        </patternFill>
-      </fill>
-      <border>
-        <left/>
-        <right/>
-        <top/>
-        <bottom/>
-      </border>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7" tint="0.59996337778862885"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7" tint="0.39994506668294322"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FF00B0F0"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FF0070C0"/>
-        </patternFill>
-      </fill>
-    </dxf>
     <dxf>
       <font>
         <color rgb="FF006100"/>
@@ -2774,7 +2642,28 @@
     <dxf>
       <fill>
         <patternFill>
-          <bgColor theme="5"/>
+          <bgColor rgb="FF00B0F0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7" tint="0.39994506668294322"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7" tint="0.59996337778862885"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="0"/>
         </patternFill>
       </fill>
       <border>
@@ -2794,6 +2683,47 @@
     <dxf>
       <fill>
         <patternFill>
+          <bgColor theme="5"/>
+        </patternFill>
+      </fill>
+      <border>
+        <left/>
+        <right/>
+        <top/>
+        <bottom/>
+      </border>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FF0070C0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FF00B0F0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7" tint="0.39994506668294322"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7" tint="0.59996337778862885"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
           <bgColor theme="0"/>
         </patternFill>
       </fill>
@@ -2807,23 +2737,22 @@
     <dxf>
       <fill>
         <patternFill>
-          <bgColor theme="7" tint="0.59996337778862885"/>
+          <bgColor theme="5" tint="0.59996337778862885"/>
         </patternFill>
       </fill>
     </dxf>
     <dxf>
       <fill>
         <patternFill>
-          <bgColor theme="7" tint="0.39994506668294322"/>
+          <bgColor theme="5"/>
         </patternFill>
       </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FF00B0F0"/>
-        </patternFill>
-      </fill>
+      <border>
+        <left/>
+        <right/>
+        <top/>
+        <bottom/>
+      </border>
     </dxf>
     <dxf>
       <fill>
@@ -4440,62 +4369,62 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="200" t="s">
+      <c r="A1" s="268" t="s">
         <v>60</v>
       </c>
-      <c r="B1" s="201"/>
-      <c r="C1" s="201"/>
-      <c r="D1" s="201"/>
-      <c r="E1" s="201"/>
-      <c r="F1" s="201"/>
-      <c r="G1" s="201"/>
-      <c r="H1" s="201"/>
-      <c r="I1" s="202"/>
+      <c r="B1" s="269"/>
+      <c r="C1" s="269"/>
+      <c r="D1" s="269"/>
+      <c r="E1" s="269"/>
+      <c r="F1" s="269"/>
+      <c r="G1" s="269"/>
+      <c r="H1" s="269"/>
+      <c r="I1" s="270"/>
     </row>
     <row r="2" spans="1:13" ht="51" x14ac:dyDescent="0.2">
-      <c r="A2" s="199" t="s">
+      <c r="A2" s="267" t="s">
         <v>61</v>
       </c>
-      <c r="B2" s="199"/>
-      <c r="C2" s="199"/>
-      <c r="D2" s="199"/>
-      <c r="E2" s="199"/>
-      <c r="F2" s="199"/>
-      <c r="G2" s="199"/>
-      <c r="H2" s="199"/>
-      <c r="I2" s="199"/>
+      <c r="B2" s="267"/>
+      <c r="C2" s="267"/>
+      <c r="D2" s="267"/>
+      <c r="E2" s="267"/>
+      <c r="F2" s="267"/>
+      <c r="G2" s="267"/>
+      <c r="H2" s="267"/>
+      <c r="I2" s="267"/>
       <c r="J2" s="165" t="s">
         <v>62</v>
       </c>
     </row>
     <row r="3" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A3" s="199" t="s">
+      <c r="A3" s="267" t="s">
         <v>63</v>
       </c>
-      <c r="B3" s="199"/>
-      <c r="C3" s="199"/>
-      <c r="D3" s="199"/>
-      <c r="E3" s="199"/>
-      <c r="F3" s="199"/>
-      <c r="G3" s="199"/>
-      <c r="H3" s="199"/>
-      <c r="I3" s="199"/>
+      <c r="B3" s="267"/>
+      <c r="C3" s="267"/>
+      <c r="D3" s="267"/>
+      <c r="E3" s="267"/>
+      <c r="F3" s="267"/>
+      <c r="G3" s="267"/>
+      <c r="H3" s="267"/>
+      <c r="I3" s="267"/>
       <c r="J3" s="166" t="s">
         <v>64</v>
       </c>
     </row>
     <row r="4" spans="1:13" ht="68" x14ac:dyDescent="0.2">
-      <c r="A4" s="199" t="s">
+      <c r="A4" s="267" t="s">
         <v>65</v>
       </c>
-      <c r="B4" s="199"/>
-      <c r="C4" s="199"/>
-      <c r="D4" s="199"/>
-      <c r="E4" s="199"/>
-      <c r="F4" s="199"/>
-      <c r="G4" s="199"/>
-      <c r="H4" s="199"/>
-      <c r="I4" s="199"/>
+      <c r="B4" s="267"/>
+      <c r="C4" s="267"/>
+      <c r="D4" s="267"/>
+      <c r="E4" s="267"/>
+      <c r="F4" s="267"/>
+      <c r="G4" s="267"/>
+      <c r="H4" s="267"/>
+      <c r="I4" s="267"/>
       <c r="J4" s="165" t="s">
         <v>66</v>
       </c>
@@ -4532,18 +4461,18 @@
       <c r="M6" s="72"/>
     </row>
     <row r="7" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A7" s="205" t="s">
+      <c r="A7" s="273" t="s">
         <v>69</v>
       </c>
-      <c r="B7" s="206"/>
-      <c r="C7" s="206"/>
-      <c r="D7" s="206"/>
-      <c r="E7" s="206"/>
-      <c r="F7" s="207"/>
-      <c r="G7" s="203" t="s">
+      <c r="B7" s="274"/>
+      <c r="C7" s="274"/>
+      <c r="D7" s="274"/>
+      <c r="E7" s="274"/>
+      <c r="F7" s="275"/>
+      <c r="G7" s="271" t="s">
         <v>70</v>
       </c>
-      <c r="H7" s="204"/>
+      <c r="H7" s="272"/>
     </row>
     <row r="8" spans="1:13" ht="17" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A8" s="164"/>
@@ -4618,11 +4547,11 @@
       <c r="M10" s="85"/>
     </row>
     <row r="11" spans="1:13" s="77" customFormat="1" ht="17" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="197" t="s">
+      <c r="A11" s="265" t="s">
         <v>81</v>
       </c>
-      <c r="B11" s="198"/>
-      <c r="C11" s="198"/>
+      <c r="B11" s="266"/>
+      <c r="C11" s="266"/>
       <c r="D11" s="73"/>
       <c r="E11" s="73"/>
       <c r="F11" s="154"/>
@@ -4649,7 +4578,7 @@
       <c r="E12" s="73">
         <v>1</v>
       </c>
-      <c r="F12" s="193">
+      <c r="F12" s="261">
         <f>_xlfn.STDEV.P(E12:E15)</f>
         <v>4.3301270189221976E-3</v>
       </c>
@@ -4686,7 +4615,7 @@
       <c r="E13" s="73">
         <v>1</v>
       </c>
-      <c r="F13" s="193"/>
+      <c r="F13" s="261"/>
       <c r="G13" s="73"/>
       <c r="H13" s="76"/>
       <c r="K13" s="88" t="s">
@@ -4716,7 +4645,7 @@
       <c r="E14" s="73">
         <v>1</v>
       </c>
-      <c r="F14" s="193"/>
+      <c r="F14" s="261"/>
       <c r="G14" s="73"/>
       <c r="H14" s="76"/>
       <c r="K14" s="88" t="s">
@@ -4746,7 +4675,7 @@
       <c r="E15" s="159">
         <v>0.99</v>
       </c>
-      <c r="F15" s="194"/>
+      <c r="F15" s="262"/>
       <c r="G15" s="159"/>
       <c r="H15" s="144"/>
       <c r="K15" s="88" t="s">
@@ -4760,11 +4689,11 @@
       </c>
     </row>
     <row r="16" spans="1:13" ht="16.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A16" s="195" t="s">
+      <c r="A16" s="263" t="s">
         <v>91</v>
       </c>
-      <c r="B16" s="196"/>
-      <c r="C16" s="196"/>
+      <c r="B16" s="264"/>
+      <c r="C16" s="264"/>
       <c r="D16" s="75"/>
       <c r="E16" s="75"/>
       <c r="F16" s="153"/>
@@ -4789,7 +4718,7 @@
       <c r="E17" s="73">
         <v>0.99</v>
       </c>
-      <c r="F17" s="193">
+      <c r="F17" s="261">
         <f>_xlfn.STDEV.P(E17:E20)</f>
         <v>0</v>
       </c>
@@ -4826,7 +4755,7 @@
       <c r="E18" s="73">
         <v>0.99</v>
       </c>
-      <c r="F18" s="193"/>
+      <c r="F18" s="261"/>
       <c r="G18" s="73"/>
       <c r="H18" s="76"/>
       <c r="K18" s="88" t="s">
@@ -4856,7 +4785,7 @@
       <c r="E19" s="73">
         <v>0.99</v>
       </c>
-      <c r="F19" s="193"/>
+      <c r="F19" s="261"/>
       <c r="G19" s="73"/>
       <c r="H19" s="76"/>
       <c r="K19" s="88" t="s">
@@ -4886,7 +4815,7 @@
       <c r="E20" s="159">
         <v>0.99</v>
       </c>
-      <c r="F20" s="194"/>
+      <c r="F20" s="262"/>
       <c r="G20" s="159"/>
       <c r="H20" s="144"/>
       <c r="K20" s="88" t="s">
@@ -4900,11 +4829,11 @@
       </c>
     </row>
     <row r="21" spans="1:13" ht="16.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A21" s="195" t="s">
+      <c r="A21" s="263" t="s">
         <v>101</v>
       </c>
-      <c r="B21" s="196"/>
-      <c r="C21" s="196"/>
+      <c r="B21" s="264"/>
+      <c r="C21" s="264"/>
       <c r="D21" s="75"/>
       <c r="E21" s="75"/>
       <c r="F21" s="153"/>
@@ -4929,7 +4858,7 @@
       <c r="E22" s="73">
         <v>0.09</v>
       </c>
-      <c r="F22" s="193">
+      <c r="F22" s="261">
         <f>_xlfn.STDEV.P(E22:E26)</f>
         <v>0.14878171930717837</v>
       </c>
@@ -4966,7 +4895,7 @@
       <c r="E23" s="73">
         <v>0.4</v>
       </c>
-      <c r="F23" s="193"/>
+      <c r="F23" s="261"/>
       <c r="G23" s="73"/>
       <c r="H23" s="76"/>
       <c r="K23" s="88" t="s">
@@ -4996,7 +4925,7 @@
       <c r="E24" s="73">
         <v>0.24</v>
       </c>
-      <c r="F24" s="193"/>
+      <c r="F24" s="261"/>
       <c r="G24" s="73"/>
       <c r="H24" s="76"/>
       <c r="K24" s="88" t="s">
@@ -5026,7 +4955,7 @@
       <c r="E25" s="73">
         <v>0.01</v>
       </c>
-      <c r="F25" s="193"/>
+      <c r="F25" s="261"/>
       <c r="G25" s="73"/>
       <c r="H25" s="76"/>
       <c r="K25" s="88" t="s">
@@ -5056,7 +4985,7 @@
       <c r="E26" s="159">
         <v>0.35</v>
       </c>
-      <c r="F26" s="194"/>
+      <c r="F26" s="262"/>
       <c r="G26" s="159"/>
       <c r="H26" s="144"/>
       <c r="K26" s="88" t="s">
@@ -5070,11 +4999,11 @@
       </c>
     </row>
     <row r="27" spans="1:13" ht="17" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A27" s="195" t="s">
+      <c r="A27" s="263" t="s">
         <v>108</v>
       </c>
-      <c r="B27" s="196"/>
-      <c r="C27" s="196"/>
+      <c r="B27" s="264"/>
+      <c r="C27" s="264"/>
       <c r="D27" s="75"/>
       <c r="E27" s="75"/>
       <c r="F27" s="153"/>
@@ -5099,7 +5028,7 @@
       <c r="E28" s="73">
         <v>0.61</v>
       </c>
-      <c r="F28" s="193">
+      <c r="F28" s="261">
         <f>_xlfn.STDEV.P(E28:E29)</f>
         <v>0.13000000000000009</v>
       </c>
@@ -5139,7 +5068,7 @@
       <c r="E29" s="159">
         <v>0.87</v>
       </c>
-      <c r="F29" s="194"/>
+      <c r="F29" s="262"/>
       <c r="G29" s="159"/>
       <c r="H29" s="144"/>
       <c r="I29" s="184" t="s">
@@ -5156,11 +5085,11 @@
       </c>
     </row>
     <row r="30" spans="1:13" ht="16.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A30" s="195" t="s">
+      <c r="A30" s="263" t="s">
         <v>114</v>
       </c>
-      <c r="B30" s="196"/>
-      <c r="C30" s="196"/>
+      <c r="B30" s="264"/>
+      <c r="C30" s="264"/>
       <c r="D30" s="75"/>
       <c r="E30" s="75"/>
       <c r="F30" s="153"/>
@@ -5185,7 +5114,7 @@
       <c r="E31" s="73">
         <v>0.94</v>
       </c>
-      <c r="F31" s="193">
+      <c r="F31" s="261">
         <f>_xlfn.STDEV.P(E31:E32)</f>
         <v>2.5000000000000022E-2</v>
       </c>
@@ -5222,7 +5151,7 @@
       <c r="E32" s="159">
         <v>0.99</v>
       </c>
-      <c r="F32" s="194"/>
+      <c r="F32" s="262"/>
       <c r="G32" s="159"/>
       <c r="H32" s="144"/>
       <c r="K32" s="88" t="s">
@@ -5243,24 +5172,24 @@
       <c r="K33" s="88"/>
     </row>
     <row r="34" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A34" s="208" t="s">
+      <c r="A34" s="276" t="s">
         <v>118</v>
       </c>
-      <c r="B34" s="209"/>
-      <c r="C34" s="209"/>
-      <c r="D34" s="209"/>
-      <c r="E34" s="209"/>
-      <c r="F34" s="210"/>
+      <c r="B34" s="277"/>
+      <c r="C34" s="277"/>
+      <c r="D34" s="277"/>
+      <c r="E34" s="277"/>
+      <c r="F34" s="278"/>
       <c r="G34" s="75"/>
       <c r="H34" s="74"/>
       <c r="K34" s="88"/>
     </row>
     <row r="35" spans="1:13" ht="17" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A35" s="197" t="s">
+      <c r="A35" s="265" t="s">
         <v>119</v>
       </c>
-      <c r="B35" s="198"/>
-      <c r="C35" s="198"/>
+      <c r="B35" s="266"/>
+      <c r="C35" s="266"/>
       <c r="F35" s="182"/>
       <c r="G35" s="73"/>
       <c r="H35" s="174"/>
@@ -5301,11 +5230,11 @@
       </c>
     </row>
     <row r="37" spans="1:13" ht="16.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A37" s="195" t="s">
+      <c r="A37" s="263" t="s">
         <v>123</v>
       </c>
-      <c r="B37" s="196"/>
-      <c r="C37" s="196"/>
+      <c r="B37" s="264"/>
+      <c r="C37" s="264"/>
       <c r="D37" s="75"/>
       <c r="E37" s="75"/>
       <c r="F37" s="153"/>
@@ -5350,11 +5279,11 @@
       </c>
     </row>
     <row r="39" spans="1:13" ht="16.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A39" s="195" t="s">
+      <c r="A39" s="263" t="s">
         <v>126</v>
       </c>
-      <c r="B39" s="196"/>
-      <c r="C39" s="196"/>
+      <c r="B39" s="264"/>
+      <c r="C39" s="264"/>
       <c r="D39" s="75"/>
       <c r="E39" s="75"/>
       <c r="F39" s="153"/>
@@ -5399,12 +5328,12 @@
       </c>
     </row>
     <row r="41" spans="1:13" ht="16.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A41" s="195" t="s">
+      <c r="A41" s="263" t="s">
         <v>128</v>
       </c>
-      <c r="B41" s="196"/>
-      <c r="C41" s="196"/>
-      <c r="D41" s="196"/>
+      <c r="B41" s="264"/>
+      <c r="C41" s="264"/>
+      <c r="D41" s="264"/>
       <c r="E41" s="75"/>
       <c r="F41" s="153"/>
       <c r="G41" s="75"/>
@@ -5448,11 +5377,11 @@
       </c>
     </row>
     <row r="43" spans="1:13" ht="16.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A43" s="195" t="s">
+      <c r="A43" s="263" t="s">
         <v>131</v>
       </c>
-      <c r="B43" s="196"/>
-      <c r="C43" s="196"/>
+      <c r="B43" s="264"/>
+      <c r="C43" s="264"/>
       <c r="D43" s="177"/>
       <c r="E43" s="75"/>
       <c r="F43" s="153"/>
@@ -5479,7 +5408,7 @@
       <c r="E44" s="73">
         <v>0.95</v>
       </c>
-      <c r="F44" s="193">
+      <c r="F44" s="261">
         <f>_xlfn.STDEV.P(E44:E45)</f>
         <v>5.0000000000000044E-3</v>
       </c>
@@ -5516,7 +5445,7 @@
       <c r="E45" s="159">
         <v>0.94</v>
       </c>
-      <c r="F45" s="194"/>
+      <c r="F45" s="262"/>
       <c r="G45" s="159"/>
       <c r="H45" s="144"/>
       <c r="K45" s="88" t="s">
@@ -5530,11 +5459,11 @@
       </c>
     </row>
     <row r="46" spans="1:13" ht="16.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A46" s="195" t="s">
+      <c r="A46" s="263" t="s">
         <v>135</v>
       </c>
-      <c r="B46" s="196"/>
-      <c r="C46" s="196"/>
+      <c r="B46" s="264"/>
+      <c r="C46" s="264"/>
       <c r="D46" s="177"/>
       <c r="E46" s="75"/>
       <c r="F46" s="153"/>
@@ -5559,7 +5488,7 @@
       <c r="E47" s="73">
         <v>0.94</v>
       </c>
-      <c r="F47" s="193">
+      <c r="F47" s="261">
         <f>_xlfn.STDEV.P(E47:E48)</f>
         <v>0.28499999999999986</v>
       </c>
@@ -5596,7 +5525,7 @@
       <c r="E48" s="159">
         <v>0.37</v>
       </c>
-      <c r="F48" s="194"/>
+      <c r="F48" s="262"/>
       <c r="G48" s="159"/>
       <c r="H48" s="144"/>
       <c r="K48" s="88" t="s">
@@ -5615,12 +5544,12 @@
       <c r="H49" s="76"/>
     </row>
     <row r="50" spans="1:13" ht="17" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A50" s="208" t="s">
+      <c r="A50" s="276" t="s">
         <v>138</v>
       </c>
-      <c r="B50" s="209"/>
-      <c r="C50" s="209"/>
-      <c r="D50" s="209"/>
+      <c r="B50" s="277"/>
+      <c r="C50" s="277"/>
+      <c r="D50" s="277"/>
       <c r="E50" s="75"/>
       <c r="F50" s="153"/>
       <c r="G50" s="75"/>
@@ -5628,12 +5557,12 @@
       <c r="K50" s="88"/>
     </row>
     <row r="51" spans="1:13" ht="17" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A51" s="197" t="s">
+      <c r="A51" s="265" t="s">
         <v>139</v>
       </c>
-      <c r="B51" s="198"/>
-      <c r="C51" s="198"/>
-      <c r="D51" s="198"/>
+      <c r="B51" s="266"/>
+      <c r="C51" s="266"/>
+      <c r="D51" s="266"/>
       <c r="F51" s="182"/>
       <c r="H51" s="76"/>
       <c r="K51" s="89" t="s">
@@ -10608,7 +10537,7 @@
         <v>184</v>
       </c>
       <c r="C22" s="133" t="s">
-        <v>185</v>
+        <v>433</v>
       </c>
       <c r="D22" s="98"/>
       <c r="E22" s="100">
@@ -11342,16 +11271,16 @@
       <c r="K48" s="96" t="s">
         <v>33</v>
       </c>
-      <c r="L48" s="214" t="s">
+      <c r="L48" s="196" t="s">
         <v>393</v>
       </c>
-      <c r="M48" s="211" t="s">
+      <c r="M48" s="193" t="s">
         <v>392</v>
       </c>
-      <c r="N48" s="214" t="s">
+      <c r="N48" s="196" t="s">
         <v>394</v>
       </c>
-      <c r="O48" s="211" t="s">
+      <c r="O48" s="193" t="s">
         <v>395</v>
       </c>
       <c r="P48" s="93" t="s">
@@ -11389,16 +11318,16 @@
       <c r="K49" s="112">
         <v>0</v>
       </c>
-      <c r="L49" s="217">
-        <v>0</v>
-      </c>
-      <c r="M49" s="217">
-        <v>0</v>
-      </c>
-      <c r="N49" s="217">
-        <v>0</v>
-      </c>
-      <c r="O49" s="217">
+      <c r="L49" s="199">
+        <v>0</v>
+      </c>
+      <c r="M49" s="199">
+        <v>0</v>
+      </c>
+      <c r="N49" s="199">
+        <v>0</v>
+      </c>
+      <c r="O49" s="199">
         <v>0</v>
       </c>
       <c r="P49" s="93" t="s">
@@ -11436,16 +11365,16 @@
       <c r="K50" s="112">
         <v>1</v>
       </c>
-      <c r="L50" s="217">
-        <v>1</v>
-      </c>
-      <c r="M50" s="217">
-        <v>1</v>
-      </c>
-      <c r="N50" s="217">
-        <v>1</v>
-      </c>
-      <c r="O50" s="217">
+      <c r="L50" s="199">
+        <v>1</v>
+      </c>
+      <c r="M50" s="199">
+        <v>1</v>
+      </c>
+      <c r="N50" s="199">
+        <v>1</v>
+      </c>
+      <c r="O50" s="199">
         <v>1</v>
       </c>
       <c r="P50" s="93" t="s">
@@ -11483,16 +11412,16 @@
       <c r="K51" s="112">
         <v>0</v>
       </c>
-      <c r="L51" s="217">
-        <v>0</v>
-      </c>
-      <c r="M51" s="217">
-        <v>0</v>
-      </c>
-      <c r="N51" s="217">
-        <v>0</v>
-      </c>
-      <c r="O51" s="217">
+      <c r="L51" s="199">
+        <v>0</v>
+      </c>
+      <c r="M51" s="199">
+        <v>0</v>
+      </c>
+      <c r="N51" s="199">
+        <v>0</v>
+      </c>
+      <c r="O51" s="199">
         <v>0</v>
       </c>
       <c r="P51" s="93" t="s">
@@ -11530,16 +11459,16 @@
       <c r="K52" s="113">
         <v>0</v>
       </c>
-      <c r="L52" s="216">
-        <v>0</v>
-      </c>
-      <c r="M52" s="216">
-        <v>0</v>
-      </c>
-      <c r="N52" s="216">
-        <v>0</v>
-      </c>
-      <c r="O52" s="216">
+      <c r="L52" s="198">
+        <v>0</v>
+      </c>
+      <c r="M52" s="198">
+        <v>0</v>
+      </c>
+      <c r="N52" s="198">
+        <v>0</v>
+      </c>
+      <c r="O52" s="198">
         <v>0</v>
       </c>
       <c r="P52" s="102" t="s">
@@ -11574,19 +11503,19 @@
         <f>SUM(K49:K52)</f>
         <v>1</v>
       </c>
-      <c r="L53" s="217">
+      <c r="L53" s="199">
         <f t="shared" ref="L53:O53" si="6">SUM(L49:L52)</f>
         <v>1</v>
       </c>
-      <c r="M53" s="217">
+      <c r="M53" s="199">
         <f t="shared" si="6"/>
         <v>1</v>
       </c>
-      <c r="N53" s="217">
+      <c r="N53" s="199">
         <f t="shared" si="6"/>
         <v>1</v>
       </c>
-      <c r="O53" s="217">
+      <c r="O53" s="199">
         <f t="shared" si="6"/>
         <v>1</v>
       </c>
@@ -11617,19 +11546,19 @@
         <f t="shared" si="7"/>
         <v>1</v>
       </c>
-      <c r="L54" s="211">
+      <c r="L54" s="193">
         <f t="shared" ref="L54:O54" si="8">SUMPRODUCT($E49:$E52, L49:L52)</f>
         <v>1</v>
       </c>
-      <c r="M54" s="211">
+      <c r="M54" s="193">
         <f t="shared" si="8"/>
         <v>1</v>
       </c>
-      <c r="N54" s="211">
+      <c r="N54" s="193">
         <f t="shared" si="8"/>
         <v>1</v>
       </c>
-      <c r="O54" s="211">
+      <c r="O54" s="193">
         <f t="shared" si="8"/>
         <v>1</v>
       </c>
@@ -11688,7 +11617,7 @@
       <c r="J58" s="96" t="s">
         <v>35</v>
       </c>
-      <c r="K58" s="211" t="s">
+      <c r="K58" s="193" t="s">
         <v>388</v>
       </c>
       <c r="L58" s="93" t="s">
@@ -11700,7 +11629,7 @@
         <v>230</v>
       </c>
       <c r="C59" s="133" t="s">
-        <v>231</v>
+        <v>233</v>
       </c>
       <c r="D59" s="98"/>
       <c r="E59" s="100">
@@ -11723,7 +11652,7 @@
       <c r="J59" s="101">
         <v>0.99399999999999999</v>
       </c>
-      <c r="K59" s="212">
+      <c r="K59" s="194">
         <v>1</v>
       </c>
       <c r="L59" s="93" t="s">
@@ -11735,7 +11664,7 @@
         <v>232</v>
       </c>
       <c r="C60" s="136" t="s">
-        <v>233</v>
+        <v>231</v>
       </c>
       <c r="D60" s="98"/>
       <c r="E60" s="100">
@@ -11758,7 +11687,7 @@
       <c r="J60" s="104">
         <v>6.0000000000000001E-3</v>
       </c>
-      <c r="K60" s="213">
+      <c r="K60" s="195">
         <v>0</v>
       </c>
       <c r="L60" s="102" t="s">
@@ -11789,7 +11718,7 @@
         <f>SUM(J59:J60)</f>
         <v>1</v>
       </c>
-      <c r="K61" s="212">
+      <c r="K61" s="194">
         <f>SUM(K59:K60)</f>
         <v>1</v>
       </c>
@@ -11817,7 +11746,7 @@
         <f>SUMPRODUCT($E59:$E60, J59:J60)</f>
         <v>0.99399999999999999</v>
       </c>
-      <c r="K62" s="211">
+      <c r="K62" s="193">
         <f>SUMPRODUCT($E59:$E60, K59:K60)</f>
         <v>1</v>
       </c>
@@ -12313,16 +12242,16 @@
       <c r="K82" s="96" t="s">
         <v>43</v>
       </c>
-      <c r="L82" s="211" t="s">
+      <c r="L82" s="193" t="s">
         <v>389</v>
       </c>
-      <c r="M82" s="214" t="s">
+      <c r="M82" s="196" t="s">
         <v>387</v>
       </c>
-      <c r="N82" s="214" t="s">
+      <c r="N82" s="196" t="s">
         <v>390</v>
       </c>
-      <c r="O82" s="214" t="s">
+      <c r="O82" s="196" t="s">
         <v>391</v>
       </c>
       <c r="P82" s="93" t="s">
@@ -12360,16 +12289,16 @@
       <c r="K83" s="101">
         <v>0.63400000000000001</v>
       </c>
-      <c r="L83" s="212">
+      <c r="L83" s="194">
         <v>0.32</v>
       </c>
-      <c r="M83" s="212">
+      <c r="M83" s="194">
         <v>0.98599999999999999</v>
       </c>
-      <c r="N83" s="212">
+      <c r="N83" s="194">
         <v>0.59</v>
       </c>
-      <c r="O83" s="212">
+      <c r="O83" s="194">
         <v>0.50600000000000001</v>
       </c>
       <c r="P83" s="93" t="s">
@@ -12407,16 +12336,16 @@
       <c r="K84" s="101">
         <v>0.36599999999999999</v>
       </c>
-      <c r="L84" s="212">
+      <c r="L84" s="194">
         <v>0.68</v>
       </c>
-      <c r="M84" s="212">
+      <c r="M84" s="194">
         <v>1.4E-2</v>
       </c>
-      <c r="N84" s="212">
+      <c r="N84" s="194">
         <v>0.41</v>
       </c>
-      <c r="O84" s="212">
+      <c r="O84" s="194">
         <v>0.49399999999999999</v>
       </c>
       <c r="P84" s="93" t="s">
@@ -12454,16 +12383,16 @@
       <c r="K85" s="141">
         <v>0</v>
       </c>
-      <c r="L85" s="215">
-        <v>0</v>
-      </c>
-      <c r="M85" s="215">
-        <v>0</v>
-      </c>
-      <c r="N85" s="215">
-        <v>0</v>
-      </c>
-      <c r="O85" s="215">
+      <c r="L85" s="197">
+        <v>0</v>
+      </c>
+      <c r="M85" s="197">
+        <v>0</v>
+      </c>
+      <c r="N85" s="197">
+        <v>0</v>
+      </c>
+      <c r="O85" s="197">
         <v>0</v>
       </c>
       <c r="P85" s="146" t="s">
@@ -12504,16 +12433,16 @@
       <c r="K86" s="141">
         <v>0</v>
       </c>
-      <c r="L86" s="215">
-        <v>0</v>
-      </c>
-      <c r="M86" s="215">
-        <v>0</v>
-      </c>
-      <c r="N86" s="215">
-        <v>0</v>
-      </c>
-      <c r="O86" s="215">
+      <c r="L86" s="197">
+        <v>0</v>
+      </c>
+      <c r="M86" s="197">
+        <v>0</v>
+      </c>
+      <c r="N86" s="197">
+        <v>0</v>
+      </c>
+      <c r="O86" s="197">
         <v>0</v>
       </c>
       <c r="P86" s="146" t="s">
@@ -12554,16 +12483,16 @@
       <c r="K87" s="113">
         <v>0</v>
       </c>
-      <c r="L87" s="216">
-        <v>0</v>
-      </c>
-      <c r="M87" s="216">
-        <v>0</v>
-      </c>
-      <c r="N87" s="216">
-        <v>0</v>
-      </c>
-      <c r="O87" s="216">
+      <c r="L87" s="198">
+        <v>0</v>
+      </c>
+      <c r="M87" s="198">
+        <v>0</v>
+      </c>
+      <c r="N87" s="198">
+        <v>0</v>
+      </c>
+      <c r="O87" s="198">
         <v>0</v>
       </c>
       <c r="P87" s="102" t="s">
@@ -12598,19 +12527,19 @@
         <f>SUM(K83:K87)</f>
         <v>1</v>
       </c>
-      <c r="L88" s="217">
-        <f t="shared" ref="L88:M88" si="14">SUM(L83:L87)</f>
-        <v>1</v>
-      </c>
-      <c r="M88" s="217">
+      <c r="L88" s="199">
+        <f t="shared" ref="L88" si="14">SUM(L83:L87)</f>
+        <v>1</v>
+      </c>
+      <c r="M88" s="199">
         <f>SUM(M83:M87)</f>
         <v>1</v>
       </c>
-      <c r="N88" s="217">
+      <c r="N88" s="199">
         <f t="shared" ref="N88:O88" si="15">SUM(N83:N87)</f>
         <v>1</v>
       </c>
-      <c r="O88" s="217">
+      <c r="O88" s="199">
         <f t="shared" si="15"/>
         <v>1</v>
       </c>
@@ -12641,19 +12570,19 @@
         <f>SUMPRODUCT($E83:$E87, K83:K87)</f>
         <v>0.36599999999999999</v>
       </c>
-      <c r="L89" s="211">
+      <c r="L89" s="193">
         <f>SUMPRODUCT($E83:$E87, L83:L87)</f>
         <v>0.68</v>
       </c>
-      <c r="M89" s="211">
+      <c r="M89" s="193">
         <f>SUMPRODUCT($E83:$E87, M83:M87)</f>
         <v>1.4E-2</v>
       </c>
-      <c r="N89" s="211">
+      <c r="N89" s="193">
         <f t="shared" ref="N89:O89" si="17">SUMPRODUCT($E83:$E87, N83:N87)</f>
         <v>0.41</v>
       </c>
-      <c r="O89" s="211">
+      <c r="O89" s="193">
         <f t="shared" si="17"/>
         <v>0.49399999999999999</v>
       </c>
@@ -13931,7 +13860,7 @@
         <v>327</v>
       </c>
       <c r="C141" s="136" t="s">
-        <v>328</v>
+        <v>434</v>
       </c>
       <c r="D141" s="98"/>
       <c r="E141" s="100">
@@ -14790,67 +14719,67 @@
       <formula>1.99</formula>
       <formula>2.01</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="14" priority="25" operator="between">
+    <cfRule type="cellIs" dxfId="14" priority="30" operator="between">
+      <formula>-0.99</formula>
+      <formula>-1.01</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="13" priority="29" operator="between">
+      <formula>-0.01</formula>
+      <formula>-0.99</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="12" priority="28" operator="between">
+      <formula>-0.01</formula>
+      <formula>0.01</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="11" priority="27" operator="between">
+      <formula>0.01</formula>
+      <formula>0.99</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="10" priority="26" operator="between">
+      <formula>0.99</formula>
+      <formula>1.01</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="9" priority="25" operator="between">
       <formula>1.01</formula>
       <formula>1.99</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="13" priority="26" operator="between">
+  </conditionalFormatting>
+  <conditionalFormatting sqref="G7">
+    <cfRule type="cellIs" dxfId="8" priority="1" operator="between">
+      <formula>1.99</formula>
+      <formula>2.01</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="7" priority="7" operator="between">
+      <formula>-0.99</formula>
+      <formula>-1.01</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="6" priority="6" operator="between">
+      <formula>-0.01</formula>
+      <formula>-0.99</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="5" priority="5" operator="between">
+      <formula>-0.01</formula>
+      <formula>0.01</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="4" priority="4" operator="between">
+      <formula>0.01</formula>
+      <formula>0.99</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="3" priority="3" operator="between">
       <formula>0.99</formula>
       <formula>1.01</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="12" priority="27" operator="between">
-      <formula>0.01</formula>
-      <formula>0.99</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="11" priority="28" operator="between">
-      <formula>-0.01</formula>
-      <formula>0.01</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="10" priority="29" operator="between">
-      <formula>-0.01</formula>
-      <formula>-0.99</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="9" priority="30" operator="between">
-      <formula>-0.99</formula>
-      <formula>-1.01</formula>
+    <cfRule type="cellIs" dxfId="2" priority="2" operator="between">
+      <formula>1.01</formula>
+      <formula>1.99</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="M8:M9">
-    <cfRule type="containsText" dxfId="8" priority="31" operator="containsText" text="FALSE">
+    <cfRule type="containsText" dxfId="1" priority="31" operator="containsText" text="FALSE">
       <formula>NOT(ISERROR(SEARCH("FALSE",M8)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="7" priority="32" operator="containsText" text="TRUE">
+    <cfRule type="containsText" dxfId="0" priority="32" operator="containsText" text="TRUE">
       <formula>NOT(ISERROR(SEARCH("TRUE",M8)))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="G7">
-    <cfRule type="cellIs" dxfId="6" priority="1" operator="between">
-      <formula>1.99</formula>
-      <formula>2.01</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="5" priority="2" operator="between">
-      <formula>1.01</formula>
-      <formula>1.99</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="4" priority="3" operator="between">
-      <formula>0.99</formula>
-      <formula>1.01</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="3" priority="4" operator="between">
-      <formula>0.01</formula>
-      <formula>0.99</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="2" priority="5" operator="between">
-      <formula>-0.01</formula>
-      <formula>0.01</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="1" priority="6" operator="between">
-      <formula>-0.01</formula>
-      <formula>-0.99</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="0" priority="7" operator="between">
-      <formula>-0.99</formula>
-      <formula>-1.01</formula>
     </cfRule>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -14964,7 +14893,7 @@
       <c r="J7" s="5" t="s">
         <v>75</v>
       </c>
-      <c r="K7" s="296" t="s">
+      <c r="K7" s="255" t="s">
         <v>377</v>
       </c>
       <c r="M7" s="58"/>
@@ -14978,11 +14907,11 @@
     </row>
     <row r="8" spans="1:22" x14ac:dyDescent="0.2">
       <c r="A8" s="5"/>
-      <c r="B8" s="294" t="s">
+      <c r="B8" s="253" t="s">
         <v>80</v>
       </c>
-      <c r="C8" s="294"/>
-      <c r="D8" s="294"/>
+      <c r="C8" s="253"/>
+      <c r="D8" s="253"/>
       <c r="E8" s="5"/>
       <c r="F8" s="5"/>
       <c r="G8" s="3"/>
@@ -15001,13 +14930,13 @@
       </c>
     </row>
     <row r="9" spans="1:22" x14ac:dyDescent="0.2">
-      <c r="A9" s="232" t="s">
+      <c r="A9" s="210" t="s">
         <v>24</v>
       </c>
       <c r="B9" s="22" t="s">
         <v>150</v>
       </c>
-      <c r="C9" s="233">
+      <c r="C9" s="211">
         <v>4</v>
       </c>
       <c r="D9" s="21">
@@ -15022,17 +14951,17 @@
       <c r="G9" s="22" t="s">
         <v>378</v>
       </c>
-      <c r="H9" s="234">
+      <c r="H9" s="212">
         <v>-4.54</v>
       </c>
-      <c r="I9" s="234">
+      <c r="I9" s="212">
         <v>-3.89</v>
       </c>
-      <c r="J9" s="234">
+      <c r="J9" s="212">
         <f>I9-H9</f>
         <v>0.64999999999999991</v>
       </c>
-      <c r="K9" s="235" t="s">
+      <c r="K9" s="213" t="s">
         <v>379</v>
       </c>
       <c r="M9" s="57" t="s">
@@ -15063,13 +14992,13 @@
       </c>
     </row>
     <row r="10" spans="1:22" x14ac:dyDescent="0.2">
-      <c r="A10" s="280" t="s">
+      <c r="A10" s="243" t="s">
         <v>25</v>
       </c>
       <c r="B10" s="19" t="s">
         <v>174</v>
       </c>
-      <c r="C10" s="277">
+      <c r="C10" s="240">
         <v>5</v>
       </c>
       <c r="D10" s="18">
@@ -15084,17 +15013,17 @@
       <c r="G10" s="19" t="s">
         <v>378</v>
       </c>
-      <c r="H10" s="278">
+      <c r="H10" s="241">
         <v>-8.85</v>
       </c>
-      <c r="I10" s="278">
+      <c r="I10" s="241">
         <v>-8.09</v>
       </c>
-      <c r="J10" s="278">
+      <c r="J10" s="241">
         <f t="shared" ref="J10:J12" si="0">I10-H10</f>
         <v>0.75999999999999979</v>
       </c>
-      <c r="K10" s="297" t="s">
+      <c r="K10" s="256" t="s">
         <v>381</v>
       </c>
       <c r="M10" s="57" t="s">
@@ -15125,13 +15054,13 @@
       </c>
     </row>
     <row r="11" spans="1:22" x14ac:dyDescent="0.2">
-      <c r="A11" s="232" t="s">
+      <c r="A11" s="210" t="s">
         <v>26</v>
       </c>
       <c r="B11" s="22" t="s">
         <v>174</v>
       </c>
-      <c r="C11" s="233">
+      <c r="C11" s="211">
         <v>5</v>
       </c>
       <c r="D11" s="21">
@@ -15146,17 +15075,17 @@
       <c r="G11" s="22" t="s">
         <v>378</v>
       </c>
-      <c r="H11" s="234">
+      <c r="H11" s="212">
         <v>-5.78</v>
       </c>
-      <c r="I11" s="234">
+      <c r="I11" s="212">
         <v>-4.83</v>
       </c>
-      <c r="J11" s="234">
+      <c r="J11" s="212">
         <f t="shared" si="0"/>
         <v>0.95000000000000018</v>
       </c>
-      <c r="K11" s="298" t="s">
+      <c r="K11" s="257" t="s">
         <v>381</v>
       </c>
       <c r="M11" s="57" t="s">
@@ -15196,29 +15125,29 @@
       <c r="C12" s="13">
         <v>3</v>
       </c>
-      <c r="D12" s="239">
+      <c r="D12" s="14">
         <v>0.09</v>
       </c>
-      <c r="E12" s="240">
+      <c r="E12" s="15">
         <v>0.09</v>
       </c>
-      <c r="F12" s="239">
-        <v>0</v>
-      </c>
-      <c r="G12" s="241" t="s">
+      <c r="F12" s="14">
+        <v>0</v>
+      </c>
+      <c r="G12" s="24" t="s">
         <v>383</v>
       </c>
-      <c r="H12" s="218">
+      <c r="H12" s="10">
         <v>-4.42</v>
       </c>
-      <c r="I12" s="218">
+      <c r="I12" s="10">
         <v>-4.1399999999999997</v>
       </c>
-      <c r="J12" s="218">
+      <c r="J12" s="10">
         <f t="shared" si="0"/>
         <v>0.28000000000000025</v>
       </c>
-      <c r="K12" s="299" t="s">
+      <c r="K12" s="51" t="s">
         <v>381</v>
       </c>
       <c r="M12" s="57" t="s">
@@ -15280,7 +15209,7 @@
         <f>I13-H13</f>
         <v>0.37000000000000099</v>
       </c>
-      <c r="K13" s="299" t="s">
+      <c r="K13" s="51" t="s">
         <v>381</v>
       </c>
       <c r="M13" s="61" t="s">
@@ -15312,31 +15241,30 @@
     </row>
     <row r="14" spans="1:22" ht="17" thickTop="1" x14ac:dyDescent="0.2">
       <c r="A14" s="11"/>
-      <c r="B14" s="294" t="s">
+      <c r="B14" s="253" t="s">
         <v>200</v>
       </c>
-      <c r="C14" s="294"/>
-      <c r="D14" s="294"/>
+      <c r="C14" s="253"/>
+      <c r="D14" s="253"/>
       <c r="E14" s="15"/>
       <c r="F14" s="14"/>
       <c r="G14" s="24"/>
       <c r="H14" s="10"/>
       <c r="I14" s="10"/>
       <c r="J14" s="10"/>
-      <c r="K14" s="245"/>
       <c r="M14" s="58"/>
       <c r="N14" s="58"/>
       <c r="O14" s="15"/>
       <c r="P14" s="10"/>
     </row>
     <row r="15" spans="1:22" x14ac:dyDescent="0.2">
-      <c r="A15" s="232" t="s">
+      <c r="A15" s="210" t="s">
         <v>30</v>
       </c>
       <c r="B15" s="22" t="s">
         <v>201</v>
       </c>
-      <c r="C15" s="233">
+      <c r="C15" s="211">
         <v>2</v>
       </c>
       <c r="D15" s="21">
@@ -15351,17 +15279,17 @@
       <c r="G15" s="45" t="s">
         <v>120</v>
       </c>
-      <c r="H15" s="234">
+      <c r="H15" s="212">
         <v>-8.31</v>
       </c>
-      <c r="I15" s="234">
+      <c r="I15" s="212">
         <v>-7.48</v>
       </c>
-      <c r="J15" s="235">
+      <c r="J15" s="213">
         <f>I15-H15</f>
         <v>0.83000000000000007</v>
       </c>
-      <c r="K15" s="292" t="s">
+      <c r="K15" s="251" t="s">
         <v>379</v>
       </c>
       <c r="M15" s="57" t="s">
@@ -15392,38 +15320,38 @@
       </c>
     </row>
     <row r="16" spans="1:22" x14ac:dyDescent="0.2">
-      <c r="A16" s="268" t="s">
+      <c r="A16" s="231" t="s">
         <v>31</v>
       </c>
-      <c r="B16" s="269" t="s">
+      <c r="B16" s="232" t="s">
         <v>207</v>
       </c>
-      <c r="C16" s="270">
+      <c r="C16" s="233">
         <v>3</v>
       </c>
-      <c r="D16" s="271">
-        <v>1</v>
-      </c>
-      <c r="E16" s="272">
-        <v>1</v>
-      </c>
-      <c r="F16" s="271">
-        <v>0</v>
-      </c>
-      <c r="G16" s="273" t="s">
+      <c r="D16" s="234">
+        <v>1</v>
+      </c>
+      <c r="E16" s="235">
+        <v>1</v>
+      </c>
+      <c r="F16" s="234">
+        <v>0</v>
+      </c>
+      <c r="G16" s="236" t="s">
         <v>120</v>
       </c>
-      <c r="H16" s="274">
+      <c r="H16" s="237">
         <v>-3.82</v>
       </c>
-      <c r="I16" s="274">
+      <c r="I16" s="237">
         <v>-3.4</v>
       </c>
-      <c r="J16" s="281">
+      <c r="J16" s="244">
         <f t="shared" ref="J16:J17" si="3">I16-H16</f>
         <v>0.41999999999999993</v>
       </c>
-      <c r="K16" s="300" t="s">
+      <c r="K16" s="258" t="s">
         <v>379</v>
       </c>
       <c r="M16" s="57" t="s">
@@ -15485,7 +15413,7 @@
         <f t="shared" si="3"/>
         <v>0.94000000000000039</v>
       </c>
-      <c r="K17" s="245" t="s">
+      <c r="K17" s="56" t="s">
         <v>379</v>
       </c>
       <c r="M17" s="57" t="s">
@@ -15516,45 +15444,44 @@
       </c>
     </row>
     <row r="18" spans="1:22" x14ac:dyDescent="0.2">
-      <c r="A18" s="236" t="s">
+      <c r="A18" s="11" t="s">
         <v>33</v>
       </c>
-      <c r="B18" s="237" t="s">
+      <c r="B18" s="12" t="s">
         <v>216</v>
       </c>
-      <c r="C18" s="238">
+      <c r="C18" s="13">
         <v>4</v>
       </c>
-      <c r="D18" s="239">
+      <c r="D18" s="14">
         <v>1.61</v>
       </c>
-      <c r="E18" s="240">
-        <v>1</v>
-      </c>
-      <c r="F18" s="239">
+      <c r="E18" s="15">
+        <v>1</v>
+      </c>
+      <c r="F18" s="14">
         <v>-0.61</v>
       </c>
-      <c r="G18" s="241" t="s">
+      <c r="G18" s="24" t="s">
         <v>383</v>
       </c>
-      <c r="H18" s="218">
+      <c r="H18" s="10">
         <v>-5.44</v>
       </c>
-      <c r="I18" s="218">
+      <c r="I18" s="10">
         <v>-4.46</v>
       </c>
       <c r="J18" s="23">
         <f>I18-H18</f>
         <v>0.98000000000000043</v>
       </c>
-      <c r="K18" s="291" t="s">
+      <c r="K18" s="56" t="s">
         <v>379</v>
       </c>
-      <c r="L18" s="242"/>
-      <c r="M18" s="220" t="s">
+      <c r="M18" s="57" t="s">
         <v>33</v>
       </c>
-      <c r="N18" s="243" t="s">
+      <c r="N18" s="58" t="s">
         <v>380</v>
       </c>
       <c r="O18" s="15">
@@ -15579,52 +15506,52 @@
       </c>
     </row>
     <row r="19" spans="1:22" x14ac:dyDescent="0.2">
-      <c r="A19" s="246" t="s">
+      <c r="A19" s="201" t="s">
         <v>393</v>
       </c>
-      <c r="B19" s="247" t="s">
+      <c r="B19" s="202" t="s">
         <v>216</v>
       </c>
-      <c r="C19" s="227">
+      <c r="C19" s="206">
         <v>4</v>
       </c>
-      <c r="D19" s="261">
+      <c r="D19" s="226">
         <v>1.61</v>
       </c>
-      <c r="E19" s="261">
-        <v>1</v>
-      </c>
-      <c r="F19" s="261">
+      <c r="E19" s="226">
+        <v>1</v>
+      </c>
+      <c r="F19" s="226">
         <v>-0.61</v>
       </c>
-      <c r="G19" s="227" t="s">
+      <c r="G19" s="206" t="s">
         <v>383</v>
       </c>
-      <c r="H19" s="227">
+      <c r="H19" s="206">
         <v>-6.36</v>
       </c>
-      <c r="I19" s="227">
+      <c r="I19" s="206">
         <v>-5.4</v>
       </c>
-      <c r="J19" s="227">
+      <c r="J19" s="206">
         <f>I19-H19</f>
         <v>0.96</v>
       </c>
-      <c r="K19" s="301" t="s">
+      <c r="K19" s="259" t="s">
         <v>379</v>
       </c>
-      <c r="L19" s="228"/>
-      <c r="M19" s="246" t="s">
+      <c r="L19" s="207"/>
+      <c r="M19" s="201" t="s">
         <v>393</v>
       </c>
-      <c r="N19" s="230" t="s">
+      <c r="N19" s="209" t="s">
         <v>380</v>
       </c>
-      <c r="O19" s="261">
+      <c r="O19" s="226">
         <f>E19</f>
         <v>1</v>
       </c>
-      <c r="P19" s="227">
+      <c r="P19" s="206">
         <f>J19</f>
         <v>0.96</v>
       </c>
@@ -15642,52 +15569,52 @@
       </c>
     </row>
     <row r="20" spans="1:22" x14ac:dyDescent="0.2">
-      <c r="A20" s="248" t="s">
+      <c r="A20" s="208" t="s">
         <v>392</v>
       </c>
-      <c r="B20" s="247" t="s">
+      <c r="B20" s="202" t="s">
         <v>216</v>
       </c>
-      <c r="C20" s="227">
+      <c r="C20" s="206">
         <v>4</v>
       </c>
-      <c r="D20" s="261">
+      <c r="D20" s="226">
         <v>1.61</v>
       </c>
-      <c r="E20" s="261">
-        <v>1</v>
-      </c>
-      <c r="F20" s="261">
+      <c r="E20" s="226">
+        <v>1</v>
+      </c>
+      <c r="F20" s="226">
         <v>-0.61</v>
       </c>
-      <c r="G20" s="227" t="s">
+      <c r="G20" s="206" t="s">
         <v>383</v>
       </c>
-      <c r="H20" s="227">
+      <c r="H20" s="206">
         <v>-6.88</v>
       </c>
-      <c r="I20" s="227">
+      <c r="I20" s="206">
         <v>-5.95</v>
       </c>
-      <c r="J20" s="227">
+      <c r="J20" s="206">
         <f t="shared" ref="J20:J21" si="6">I20-H20</f>
         <v>0.92999999999999972</v>
       </c>
-      <c r="K20" s="301" t="s">
+      <c r="K20" s="259" t="s">
         <v>379</v>
       </c>
-      <c r="L20" s="228"/>
-      <c r="M20" s="248" t="s">
+      <c r="L20" s="207"/>
+      <c r="M20" s="208" t="s">
         <v>392</v>
       </c>
-      <c r="N20" s="230" t="s">
+      <c r="N20" s="209" t="s">
         <v>380</v>
       </c>
-      <c r="O20" s="261">
+      <c r="O20" s="226">
         <f t="shared" ref="O20:O21" si="7">E20</f>
         <v>1</v>
       </c>
-      <c r="P20" s="227">
+      <c r="P20" s="206">
         <f>J20</f>
         <v>0.92999999999999972</v>
       </c>
@@ -15705,52 +15632,52 @@
       </c>
     </row>
     <row r="21" spans="1:22" x14ac:dyDescent="0.2">
-      <c r="A21" s="248" t="s">
+      <c r="A21" s="208" t="s">
         <v>394</v>
       </c>
-      <c r="B21" s="247" t="s">
+      <c r="B21" s="202" t="s">
         <v>216</v>
       </c>
-      <c r="C21" s="227">
+      <c r="C21" s="206">
         <v>4</v>
       </c>
-      <c r="D21" s="261">
+      <c r="D21" s="226">
         <v>1.61</v>
       </c>
-      <c r="E21" s="261">
-        <v>1</v>
-      </c>
-      <c r="F21" s="261">
+      <c r="E21" s="226">
+        <v>1</v>
+      </c>
+      <c r="F21" s="226">
         <v>-0.61</v>
       </c>
-      <c r="G21" s="227" t="s">
+      <c r="G21" s="206" t="s">
         <v>383</v>
       </c>
-      <c r="H21" s="227">
+      <c r="H21" s="206">
         <v>-5.47</v>
       </c>
-      <c r="I21" s="227">
+      <c r="I21" s="206">
         <v>-4.53</v>
       </c>
-      <c r="J21" s="227">
+      <c r="J21" s="206">
         <f t="shared" si="6"/>
         <v>0.9399999999999995</v>
       </c>
-      <c r="K21" s="301" t="s">
+      <c r="K21" s="259" t="s">
         <v>379</v>
       </c>
-      <c r="L21" s="228"/>
-      <c r="M21" s="248" t="s">
+      <c r="L21" s="207"/>
+      <c r="M21" s="208" t="s">
         <v>394</v>
       </c>
-      <c r="N21" s="230" t="s">
+      <c r="N21" s="209" t="s">
         <v>380</v>
       </c>
-      <c r="O21" s="261">
+      <c r="O21" s="226">
         <f t="shared" si="7"/>
         <v>1</v>
       </c>
-      <c r="P21" s="227">
+      <c r="P21" s="206">
         <f>J21</f>
         <v>0.9399999999999995</v>
       </c>
@@ -15768,52 +15695,52 @@
       </c>
     </row>
     <row r="22" spans="1:22" ht="17" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A22" s="249" t="s">
+      <c r="A22" s="214" t="s">
         <v>395</v>
       </c>
-      <c r="B22" s="250" t="s">
+      <c r="B22" s="215" t="s">
         <v>216</v>
       </c>
-      <c r="C22" s="251">
+      <c r="C22" s="216">
         <v>4</v>
       </c>
-      <c r="D22" s="252">
+      <c r="D22" s="217">
         <v>1.61</v>
       </c>
-      <c r="E22" s="253">
-        <v>1</v>
-      </c>
-      <c r="F22" s="254">
+      <c r="E22" s="218">
+        <v>1</v>
+      </c>
+      <c r="F22" s="219">
         <v>-0.61</v>
       </c>
-      <c r="G22" s="255" t="s">
+      <c r="G22" s="220" t="s">
         <v>383</v>
       </c>
-      <c r="H22" s="256">
+      <c r="H22" s="221">
         <v>-6.33</v>
       </c>
-      <c r="I22" s="256">
+      <c r="I22" s="221">
         <v>-5.39</v>
       </c>
-      <c r="J22" s="257">
+      <c r="J22" s="222">
         <f>I22-H22</f>
         <v>0.94000000000000039</v>
       </c>
-      <c r="K22" s="301" t="s">
+      <c r="K22" s="259" t="s">
         <v>379</v>
       </c>
-      <c r="L22" s="228"/>
-      <c r="M22" s="249" t="s">
+      <c r="L22" s="207"/>
+      <c r="M22" s="214" t="s">
         <v>395</v>
       </c>
-      <c r="N22" s="230" t="s">
+      <c r="N22" s="209" t="s">
         <v>380</v>
       </c>
-      <c r="O22" s="253">
+      <c r="O22" s="218">
         <f>E22</f>
         <v>1</v>
       </c>
-      <c r="P22" s="257">
+      <c r="P22" s="222">
         <f>J22</f>
         <v>0.94000000000000039</v>
       </c>
@@ -15843,59 +15770,58 @@
       <c r="H23" s="10"/>
       <c r="I23" s="10"/>
       <c r="J23" s="10"/>
-      <c r="K23" s="245"/>
-      <c r="M23" s="221"/>
+      <c r="M23" s="200"/>
       <c r="N23" s="58"/>
       <c r="O23" s="15"/>
       <c r="P23" s="10"/>
     </row>
     <row r="24" spans="1:22" x14ac:dyDescent="0.2">
-      <c r="A24" s="222" t="s">
+      <c r="A24" s="201" t="s">
         <v>388</v>
       </c>
-      <c r="B24" s="223" t="s">
+      <c r="B24" s="202" t="s">
         <v>229</v>
       </c>
-      <c r="C24" s="224">
+      <c r="C24" s="203">
         <v>2</v>
       </c>
-      <c r="D24" s="225">
+      <c r="D24" s="204">
         <v>0.97199999999999998</v>
       </c>
-      <c r="E24" s="226">
-        <v>1</v>
-      </c>
-      <c r="F24" s="225">
+      <c r="E24" s="205">
+        <v>1</v>
+      </c>
+      <c r="F24" s="204">
         <v>0.03</v>
       </c>
-      <c r="G24" s="231" t="s">
+      <c r="G24" s="245" t="s">
         <v>120</v>
       </c>
-      <c r="H24" s="262">
+      <c r="H24" s="227">
         <v>-8.86</v>
       </c>
-      <c r="I24" s="262">
+      <c r="I24" s="227">
         <v>-8.8800000000000008</v>
       </c>
-      <c r="J24" s="262">
+      <c r="J24" s="227">
         <f>I24-H24</f>
         <v>-2.000000000000135E-2</v>
       </c>
-      <c r="K24" s="301" t="s">
+      <c r="K24" s="259" t="s">
         <v>379</v>
       </c>
-      <c r="L24" s="228"/>
-      <c r="M24" s="229" t="s">
+      <c r="L24" s="207"/>
+      <c r="M24" s="208" t="s">
         <v>388</v>
       </c>
-      <c r="N24" s="263" t="s">
+      <c r="N24" s="228" t="s">
         <v>380</v>
       </c>
-      <c r="O24" s="226">
+      <c r="O24" s="205">
         <f>E24</f>
         <v>1</v>
       </c>
-      <c r="P24" s="262">
+      <c r="P24" s="227">
         <f>J24</f>
         <v>-2.000000000000135E-2</v>
       </c>
@@ -15944,10 +15870,9 @@
         <f>I25-H25</f>
         <v>1.03</v>
       </c>
-      <c r="K25" s="245" t="s">
+      <c r="K25" s="56" t="s">
         <v>379</v>
       </c>
-      <c r="L25" s="244"/>
       <c r="M25" s="61" t="s">
         <v>35</v>
       </c>
@@ -15977,7 +15902,7 @@
     </row>
     <row r="26" spans="1:22" ht="17" thickTop="1" x14ac:dyDescent="0.2">
       <c r="A26" s="36"/>
-      <c r="B26" s="295" t="s">
+      <c r="B26" s="254" t="s">
         <v>235</v>
       </c>
       <c r="C26" s="37"/>
@@ -15988,7 +15913,6 @@
       <c r="H26" s="41"/>
       <c r="I26" s="41"/>
       <c r="J26" s="41"/>
-      <c r="K26" s="245"/>
       <c r="M26" s="58"/>
       <c r="N26" s="58"/>
       <c r="O26" s="39"/>
@@ -16026,7 +15950,7 @@
         <f>I27-H27</f>
         <v>1.8900000000000001</v>
       </c>
-      <c r="K27" s="245" t="s">
+      <c r="K27" s="56" t="s">
         <v>381</v>
       </c>
       <c r="M27" s="57" t="s">
@@ -16081,7 +16005,7 @@
       <c r="H28" s="34"/>
       <c r="I28" s="34"/>
       <c r="J28" s="43"/>
-      <c r="K28" s="245" t="s">
+      <c r="K28" s="56" t="s">
         <v>381</v>
       </c>
       <c r="M28" s="61" t="s">
@@ -16098,7 +16022,7 @@
     </row>
     <row r="29" spans="1:22" ht="17" thickTop="1" x14ac:dyDescent="0.2">
       <c r="A29" s="11"/>
-      <c r="B29" s="294" t="s">
+      <c r="B29" s="253" t="s">
         <v>245</v>
       </c>
       <c r="C29" s="9"/>
@@ -16109,55 +16033,53 @@
       <c r="H29" s="10"/>
       <c r="I29" s="10"/>
       <c r="J29" s="10"/>
-      <c r="K29" s="245"/>
       <c r="M29" s="58"/>
       <c r="N29" s="58"/>
       <c r="O29" s="9"/>
       <c r="P29" s="10"/>
     </row>
     <row r="30" spans="1:22" x14ac:dyDescent="0.2">
-      <c r="A30" s="236" t="s">
+      <c r="A30" s="11" t="s">
         <v>40</v>
       </c>
-      <c r="B30" s="237" t="s">
+      <c r="B30" s="12" t="s">
         <v>246</v>
       </c>
-      <c r="C30" s="238">
+      <c r="C30" s="13">
         <v>3</v>
       </c>
-      <c r="D30" s="239">
+      <c r="D30" s="14">
         <v>0.99</v>
       </c>
-      <c r="E30" s="240">
+      <c r="E30" s="15">
         <v>0.95</v>
       </c>
-      <c r="F30" s="239">
+      <c r="F30" s="14">
         <v>-0.04</v>
       </c>
-      <c r="G30" s="241" t="s">
+      <c r="G30" s="24" t="s">
         <v>120</v>
       </c>
-      <c r="H30" s="218">
+      <c r="H30" s="10">
         <v>-6.6</v>
       </c>
-      <c r="I30" s="218">
+      <c r="I30" s="10">
         <v>-5.78</v>
       </c>
-      <c r="J30" s="266">
+      <c r="J30" s="42">
         <f>I30-H30</f>
         <v>0.8199999999999994</v>
       </c>
-      <c r="K30" s="291" t="s">
+      <c r="K30" s="56" t="s">
         <v>379</v>
       </c>
-      <c r="L30" s="244"/>
       <c r="M30" s="57" t="s">
         <v>40</v>
       </c>
       <c r="N30" s="58" t="s">
         <v>380</v>
       </c>
-      <c r="O30" s="240">
+      <c r="O30" s="15">
         <f>E30</f>
         <v>0.95</v>
       </c>
@@ -16179,13 +16101,13 @@
       </c>
     </row>
     <row r="31" spans="1:22" x14ac:dyDescent="0.2">
-      <c r="A31" s="232" t="s">
+      <c r="A31" s="210" t="s">
         <v>41</v>
       </c>
       <c r="B31" s="22" t="s">
         <v>246</v>
       </c>
-      <c r="C31" s="233">
+      <c r="C31" s="211">
         <v>3</v>
       </c>
       <c r="D31" s="21">
@@ -16200,27 +16122,26 @@
       <c r="G31" s="45" t="s">
         <v>120</v>
       </c>
-      <c r="H31" s="234">
+      <c r="H31" s="212">
         <v>-0.64</v>
       </c>
-      <c r="I31" s="234">
+      <c r="I31" s="212">
         <v>0.03</v>
       </c>
-      <c r="J31" s="267">
+      <c r="J31" s="230">
         <f t="shared" ref="J31:J33" si="8">I31-H31</f>
         <v>0.67</v>
       </c>
-      <c r="K31" s="292" t="s">
+      <c r="K31" s="251" t="s">
         <v>379</v>
       </c>
-      <c r="L31" s="244"/>
       <c r="M31" s="57" t="s">
         <v>41</v>
       </c>
       <c r="N31" s="58" t="s">
         <v>380</v>
       </c>
-      <c r="O31" s="240">
+      <c r="O31" s="15">
         <f t="shared" ref="O31:O33" si="9">E31</f>
         <v>0.96</v>
       </c>
@@ -16242,13 +16163,13 @@
       </c>
     </row>
     <row r="32" spans="1:22" x14ac:dyDescent="0.2">
-      <c r="A32" s="276" t="s">
+      <c r="A32" s="239" t="s">
         <v>42</v>
       </c>
       <c r="B32" s="19" t="s">
         <v>255</v>
       </c>
-      <c r="C32" s="277">
+      <c r="C32" s="240">
         <v>5</v>
       </c>
       <c r="D32" s="18">
@@ -16263,27 +16184,26 @@
       <c r="G32" s="44" t="s">
         <v>383</v>
       </c>
-      <c r="H32" s="278">
+      <c r="H32" s="241">
         <v>-7.19</v>
       </c>
-      <c r="I32" s="278">
+      <c r="I32" s="241">
         <v>-6.59</v>
       </c>
-      <c r="J32" s="279">
+      <c r="J32" s="242">
         <f t="shared" si="8"/>
         <v>0.60000000000000053</v>
       </c>
-      <c r="K32" s="293" t="s">
+      <c r="K32" s="252" t="s">
         <v>379</v>
       </c>
-      <c r="L32" s="244"/>
       <c r="M32" s="57" t="s">
         <v>42</v>
       </c>
       <c r="N32" s="58" t="s">
         <v>380</v>
       </c>
-      <c r="O32" s="240">
+      <c r="O32" s="15">
         <f t="shared" si="9"/>
         <v>0.7</v>
       </c>
@@ -16305,48 +16225,47 @@
       </c>
     </row>
     <row r="33" spans="1:22" x14ac:dyDescent="0.2">
-      <c r="A33" s="236" t="s">
+      <c r="A33" s="11" t="s">
         <v>43</v>
       </c>
-      <c r="B33" s="237" t="s">
+      <c r="B33" s="12" t="s">
         <v>255</v>
       </c>
-      <c r="C33" s="238">
+      <c r="C33" s="13">
         <v>5</v>
       </c>
-      <c r="D33" s="239">
+      <c r="D33" s="14">
         <v>0.3</v>
       </c>
-      <c r="E33" s="240">
+      <c r="E33" s="15">
         <v>0.37</v>
       </c>
-      <c r="F33" s="239">
+      <c r="F33" s="14">
         <v>7.0000000000000007E-2</v>
       </c>
-      <c r="G33" s="241" t="s">
+      <c r="G33" s="24" t="s">
         <v>383</v>
       </c>
-      <c r="H33" s="218">
+      <c r="H33" s="10">
         <v>-5.94</v>
       </c>
-      <c r="I33" s="218">
+      <c r="I33" s="10">
         <v>-5.68</v>
       </c>
-      <c r="J33" s="266">
+      <c r="J33" s="42">
         <f t="shared" si="8"/>
         <v>0.26000000000000068</v>
       </c>
-      <c r="K33" s="291" t="s">
+      <c r="K33" s="56" t="s">
         <v>379</v>
       </c>
-      <c r="L33" s="244"/>
       <c r="M33" s="57" t="s">
         <v>43</v>
       </c>
       <c r="N33" s="58" t="s">
         <v>380</v>
       </c>
-      <c r="O33" s="240">
+      <c r="O33" s="15">
         <f t="shared" si="9"/>
         <v>0.37</v>
       </c>
@@ -16368,53 +16287,53 @@
       </c>
     </row>
     <row r="34" spans="1:22" x14ac:dyDescent="0.2">
-      <c r="A34" s="246" t="s">
+      <c r="A34" s="201" t="s">
         <v>389</v>
       </c>
-      <c r="B34" s="247" t="s">
+      <c r="B34" s="202" t="s">
         <v>255</v>
       </c>
-      <c r="C34" s="282">
+      <c r="C34" s="203">
         <v>5</v>
       </c>
-      <c r="D34" s="283">
-        <v>1.61</v>
-      </c>
-      <c r="E34" s="265">
-        <v>1</v>
-      </c>
-      <c r="F34" s="283">
+      <c r="D34" s="204">
+        <v>0.3</v>
+      </c>
+      <c r="E34" s="205">
+        <v>0.68</v>
+      </c>
+      <c r="F34" s="204">
         <f>E34-D34</f>
-        <v>-0.6100000000000001</v>
-      </c>
-      <c r="G34" s="284" t="s">
+        <v>0.38000000000000006</v>
+      </c>
+      <c r="G34" s="245" t="s">
         <v>383</v>
       </c>
-      <c r="H34" s="262">
+      <c r="H34" s="227">
         <v>-5.75</v>
       </c>
-      <c r="I34" s="262">
+      <c r="I34" s="227">
         <v>-5.16</v>
       </c>
-      <c r="J34" s="285">
+      <c r="J34" s="229">
         <f>I34-H34</f>
         <v>0.58999999999999986</v>
       </c>
-      <c r="K34" s="302" t="s">
+      <c r="K34" s="259" t="s">
         <v>379</v>
       </c>
-      <c r="L34" s="228"/>
-      <c r="M34" s="222" t="s">
+      <c r="L34" s="207"/>
+      <c r="M34" s="201" t="s">
         <v>389</v>
       </c>
-      <c r="N34" s="230" t="s">
+      <c r="N34" s="209" t="s">
         <v>380</v>
       </c>
-      <c r="O34" s="265">
+      <c r="O34" s="205">
         <f>E34</f>
-        <v>1</v>
-      </c>
-      <c r="P34" s="264">
+        <v>0.68</v>
+      </c>
+      <c r="P34" s="229">
         <f>J34</f>
         <v>0.58999999999999986</v>
       </c>
@@ -16432,54 +16351,54 @@
       </c>
     </row>
     <row r="35" spans="1:22" x14ac:dyDescent="0.2">
-      <c r="A35" s="246" t="s">
+      <c r="A35" s="201" t="s">
         <v>387</v>
       </c>
-      <c r="B35" s="247" t="s">
+      <c r="B35" s="202" t="s">
         <v>255</v>
       </c>
-      <c r="C35" s="282">
+      <c r="C35" s="203">
         <v>5</v>
       </c>
-      <c r="D35" s="283">
-        <v>1.61</v>
-      </c>
-      <c r="E35" s="265">
-        <v>1</v>
-      </c>
-      <c r="F35" s="283">
+      <c r="D35" s="204">
+        <v>0.3</v>
+      </c>
+      <c r="E35" s="205">
+        <v>1.4E-2</v>
+      </c>
+      <c r="F35" s="204">
         <f t="shared" ref="F35:F37" si="11">E35-D35</f>
-        <v>-0.6100000000000001</v>
-      </c>
-      <c r="G35" s="284" t="s">
+        <v>-0.28599999999999998</v>
+      </c>
+      <c r="G35" s="245" t="s">
         <v>383</v>
       </c>
-      <c r="H35" s="262">
+      <c r="H35" s="227">
         <v>-3.03</v>
       </c>
-      <c r="I35" s="262">
+      <c r="I35" s="227">
         <v>-2.94</v>
       </c>
-      <c r="J35" s="285">
+      <c r="J35" s="229">
         <f t="shared" ref="J35:J36" si="12">I35-H35</f>
         <v>8.9999999999999858E-2</v>
       </c>
-      <c r="K35" s="302" t="s">
+      <c r="K35" s="259" t="s">
         <v>379</v>
       </c>
-      <c r="L35" s="228"/>
-      <c r="M35" s="222" t="s">
+      <c r="L35" s="207"/>
+      <c r="M35" s="201" t="s">
         <v>387</v>
       </c>
-      <c r="N35" s="230" t="s">
+      <c r="N35" s="209" t="s">
         <v>380</v>
       </c>
-      <c r="O35" s="265">
-        <f t="shared" ref="O35:O36" si="13">E35</f>
-        <v>1</v>
-      </c>
-      <c r="P35" s="264">
-        <f t="shared" ref="P35:P37" si="14">J35</f>
+      <c r="O35" s="205">
+        <f>E35</f>
+        <v>1.4E-2</v>
+      </c>
+      <c r="P35" s="229">
+        <f t="shared" ref="P35:P37" si="13">J35</f>
         <v>8.9999999999999858E-2</v>
       </c>
       <c r="R35" t="s">
@@ -16496,54 +16415,54 @@
       </c>
     </row>
     <row r="36" spans="1:22" x14ac:dyDescent="0.2">
-      <c r="A36" s="246" t="s">
+      <c r="A36" s="201" t="s">
         <v>390</v>
       </c>
-      <c r="B36" s="247" t="s">
+      <c r="B36" s="202" t="s">
         <v>255</v>
       </c>
-      <c r="C36" s="282">
+      <c r="C36" s="203">
         <v>5</v>
       </c>
-      <c r="D36" s="283">
-        <v>1.61</v>
-      </c>
-      <c r="E36" s="265">
-        <v>1</v>
-      </c>
-      <c r="F36" s="283">
+      <c r="D36" s="204">
+        <v>0.3</v>
+      </c>
+      <c r="E36" s="205">
+        <v>0.41</v>
+      </c>
+      <c r="F36" s="204">
         <f t="shared" si="11"/>
-        <v>-0.6100000000000001</v>
-      </c>
-      <c r="G36" s="284" t="s">
+        <v>0.10999999999999999</v>
+      </c>
+      <c r="G36" s="245" t="s">
         <v>383</v>
       </c>
-      <c r="H36" s="262">
+      <c r="H36" s="227">
         <v>1.86</v>
       </c>
-      <c r="I36" s="262">
+      <c r="I36" s="227">
         <v>2.2400000000000002</v>
       </c>
-      <c r="J36" s="285">
+      <c r="J36" s="229">
         <f t="shared" si="12"/>
         <v>0.38000000000000012</v>
       </c>
-      <c r="K36" s="302" t="s">
+      <c r="K36" s="259" t="s">
         <v>379</v>
       </c>
-      <c r="L36" s="228"/>
-      <c r="M36" s="222" t="s">
+      <c r="L36" s="207"/>
+      <c r="M36" s="201" t="s">
         <v>390</v>
       </c>
-      <c r="N36" s="230" t="s">
+      <c r="N36" s="209" t="s">
         <v>380</v>
       </c>
-      <c r="O36" s="265">
+      <c r="O36" s="205">
+        <f t="shared" ref="O35:O36" si="14">E36</f>
+        <v>0.41</v>
+      </c>
+      <c r="P36" s="229">
         <f t="shared" si="13"/>
-        <v>1</v>
-      </c>
-      <c r="P36" s="264">
-        <f t="shared" si="14"/>
         <v>0.38000000000000012</v>
       </c>
       <c r="R36" t="s">
@@ -16560,54 +16479,54 @@
       </c>
     </row>
     <row r="37" spans="1:22" x14ac:dyDescent="0.2">
-      <c r="A37" s="258" t="s">
+      <c r="A37" s="223" t="s">
         <v>391</v>
       </c>
-      <c r="B37" s="286" t="s">
+      <c r="B37" s="246" t="s">
         <v>255</v>
       </c>
-      <c r="C37" s="287">
+      <c r="C37" s="247">
         <v>5</v>
       </c>
-      <c r="D37" s="288">
-        <v>1.61</v>
-      </c>
-      <c r="E37" s="259">
-        <v>1</v>
-      </c>
-      <c r="F37" s="288">
+      <c r="D37" s="248">
+        <v>0.3</v>
+      </c>
+      <c r="E37" s="224">
+        <v>0.49399999999999999</v>
+      </c>
+      <c r="F37" s="248">
         <f t="shared" si="11"/>
-        <v>-0.6100000000000001</v>
-      </c>
-      <c r="G37" s="289" t="s">
+        <v>0.19400000000000001</v>
+      </c>
+      <c r="G37" s="249" t="s">
         <v>383</v>
       </c>
-      <c r="H37" s="290">
+      <c r="H37" s="250">
         <v>-1.36</v>
       </c>
-      <c r="I37" s="290">
+      <c r="I37" s="250">
         <v>-0.88</v>
       </c>
-      <c r="J37" s="260">
+      <c r="J37" s="225">
         <f>I37-H37</f>
         <v>0.48000000000000009</v>
       </c>
-      <c r="K37" s="303" t="s">
+      <c r="K37" s="260" t="s">
         <v>379</v>
       </c>
-      <c r="L37" s="228"/>
-      <c r="M37" s="222" t="s">
+      <c r="L37" s="207"/>
+      <c r="M37" s="201" t="s">
         <v>391</v>
       </c>
-      <c r="N37" s="230" t="s">
+      <c r="N37" s="209" t="s">
         <v>380</v>
       </c>
-      <c r="O37" s="265">
+      <c r="O37" s="205">
         <f>E37</f>
-        <v>1</v>
-      </c>
-      <c r="P37" s="264">
-        <f t="shared" si="14"/>
+        <v>0.49399999999999999</v>
+      </c>
+      <c r="P37" s="229">
+        <f t="shared" si="13"/>
         <v>0.48000000000000009</v>
       </c>
       <c r="R37" t="s">
@@ -16624,52 +16543,51 @@
       </c>
     </row>
     <row r="38" spans="1:22" x14ac:dyDescent="0.2">
-      <c r="A38" s="268" t="s">
+      <c r="A38" s="231" t="s">
         <v>44</v>
       </c>
-      <c r="B38" s="269" t="s">
+      <c r="B38" s="232" t="s">
         <v>271</v>
       </c>
-      <c r="C38" s="270">
+      <c r="C38" s="233">
         <v>3</v>
       </c>
-      <c r="D38" s="271">
+      <c r="D38" s="234">
         <v>0.95</v>
       </c>
-      <c r="E38" s="272">
+      <c r="E38" s="235">
         <v>0.45</v>
       </c>
-      <c r="F38" s="271">
+      <c r="F38" s="234">
         <v>-0.5</v>
       </c>
-      <c r="G38" s="273" t="s">
+      <c r="G38" s="236" t="s">
         <v>120</v>
       </c>
-      <c r="H38" s="274">
+      <c r="H38" s="237">
         <v>-3.29</v>
       </c>
-      <c r="I38" s="274">
+      <c r="I38" s="237">
         <v>-2.77</v>
       </c>
-      <c r="J38" s="281">
+      <c r="J38" s="244">
         <f>I38-H38</f>
         <v>0.52</v>
       </c>
-      <c r="K38" s="300" t="s">
+      <c r="K38" s="258" t="s">
         <v>379</v>
       </c>
-      <c r="L38" s="242"/>
-      <c r="M38" s="220" t="s">
+      <c r="M38" s="57" t="s">
         <v>44</v>
       </c>
-      <c r="N38" s="243" t="s">
+      <c r="N38" s="58" t="s">
         <v>380</v>
       </c>
-      <c r="O38" s="240">
+      <c r="O38" s="15">
         <f>E38</f>
         <v>0.45</v>
       </c>
-      <c r="P38" s="219">
+      <c r="P38" s="23">
         <f>J38</f>
         <v>0.52</v>
       </c>
@@ -16718,7 +16636,7 @@
         <f>I39-H39</f>
         <v>0.71</v>
       </c>
-      <c r="K39" s="245" t="s">
+      <c r="K39" s="56" t="s">
         <v>379</v>
       </c>
       <c r="M39" s="61" t="s">
@@ -16761,7 +16679,6 @@
       <c r="H40" s="10"/>
       <c r="I40" s="10"/>
       <c r="J40" s="10"/>
-      <c r="K40" s="245"/>
       <c r="M40" s="58"/>
       <c r="N40" s="58"/>
       <c r="O40" s="15"/>
@@ -16799,7 +16716,7 @@
         <f>I41-H41</f>
         <v>0.11999999999999988</v>
       </c>
-      <c r="K41" s="245" t="s">
+      <c r="K41" s="56" t="s">
         <v>379</v>
       </c>
       <c r="M41" s="62" t="s">
@@ -16842,7 +16759,6 @@
       <c r="H42" s="10"/>
       <c r="I42" s="10"/>
       <c r="J42" s="10"/>
-      <c r="K42" s="245"/>
       <c r="M42" s="58"/>
       <c r="N42" s="58"/>
       <c r="O42" s="15"/>
@@ -16880,7 +16796,7 @@
         <f>I43-H43</f>
         <v>8.0000000000000071E-2</v>
       </c>
-      <c r="K43" s="245" t="s">
+      <c r="K43" s="56" t="s">
         <v>379</v>
       </c>
       <c r="M43" s="57" t="s">
@@ -16942,7 +16858,7 @@
         <f>I44-H44</f>
         <v>0.60999999999999988</v>
       </c>
-      <c r="K44" s="245" t="s">
+      <c r="K44" s="56" t="s">
         <v>379</v>
       </c>
       <c r="M44" s="61" t="s">
@@ -16974,7 +16890,7 @@
     </row>
     <row r="45" spans="1:22" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A45" s="11"/>
-      <c r="B45" s="294" t="s">
+      <c r="B45" s="253" t="s">
         <v>138</v>
       </c>
       <c r="C45" s="13"/>
@@ -16985,7 +16901,6 @@
       <c r="H45" s="10"/>
       <c r="I45" s="10"/>
       <c r="J45" s="10"/>
-      <c r="K45" s="245"/>
       <c r="M45" s="58"/>
       <c r="N45" s="58"/>
       <c r="O45" s="15"/>
@@ -17023,7 +16938,7 @@
         <f>I46-H46</f>
         <v>0.74000000000000021</v>
       </c>
-      <c r="K46" s="245" t="s">
+      <c r="K46" s="56" t="s">
         <v>379</v>
       </c>
       <c r="M46" s="62" t="s">
@@ -17066,45 +16981,44 @@
       <c r="H47" s="10"/>
       <c r="I47" s="10"/>
       <c r="J47" s="10"/>
-      <c r="K47" s="245"/>
       <c r="M47" s="58"/>
       <c r="N47" s="58"/>
       <c r="O47" s="47"/>
       <c r="P47" s="10"/>
     </row>
     <row r="48" spans="1:22" x14ac:dyDescent="0.2">
-      <c r="A48" s="236" t="s">
+      <c r="A48" s="11" t="s">
         <v>54</v>
       </c>
-      <c r="B48" s="237" t="s">
+      <c r="B48" s="12" t="s">
         <v>320</v>
       </c>
-      <c r="C48" s="238">
+      <c r="C48" s="13">
         <v>3</v>
       </c>
-      <c r="D48" s="239">
-        <v>0</v>
-      </c>
-      <c r="E48" s="240">
-        <v>0</v>
-      </c>
-      <c r="F48" s="239">
-        <v>0</v>
-      </c>
-      <c r="G48" s="237" t="s">
+      <c r="D48" s="14">
+        <v>0</v>
+      </c>
+      <c r="E48" s="15">
+        <v>0</v>
+      </c>
+      <c r="F48" s="14">
+        <v>0</v>
+      </c>
+      <c r="G48" s="12" t="s">
         <v>378</v>
       </c>
-      <c r="H48" s="218">
+      <c r="H48" s="10">
         <v>4.91</v>
       </c>
-      <c r="I48" s="218">
+      <c r="I48" s="10">
         <v>4.5999999999999996</v>
       </c>
-      <c r="J48" s="266">
+      <c r="J48" s="42">
         <f>I48-H48</f>
         <v>-0.3100000000000005</v>
       </c>
-      <c r="K48" s="291" t="s">
+      <c r="K48" s="56" t="s">
         <v>381</v>
       </c>
       <c r="M48" s="57" t="s">
@@ -17113,7 +17027,7 @@
       <c r="N48" s="58" t="s">
         <v>382</v>
       </c>
-      <c r="O48" s="240">
+      <c r="O48" s="15">
         <f>E48</f>
         <v>0</v>
       </c>
@@ -17135,13 +17049,13 @@
       </c>
     </row>
     <row r="49" spans="1:22" x14ac:dyDescent="0.2">
-      <c r="A49" s="232" t="s">
+      <c r="A49" s="210" t="s">
         <v>55</v>
       </c>
       <c r="B49" s="22" t="s">
         <v>320</v>
       </c>
-      <c r="C49" s="233">
+      <c r="C49" s="211">
         <v>3</v>
       </c>
       <c r="D49" s="21">
@@ -17156,17 +17070,17 @@
       <c r="G49" s="22" t="s">
         <v>378</v>
       </c>
-      <c r="H49" s="234">
+      <c r="H49" s="212">
         <v>3.43</v>
       </c>
-      <c r="I49" s="234">
+      <c r="I49" s="212">
         <v>3.42</v>
       </c>
-      <c r="J49" s="267">
+      <c r="J49" s="230">
         <f t="shared" ref="J49:J51" si="15">I49-H49</f>
         <v>-1.0000000000000231E-2</v>
       </c>
-      <c r="K49" s="292" t="s">
+      <c r="K49" s="251" t="s">
         <v>381</v>
       </c>
       <c r="M49" s="57" t="s">
@@ -17175,7 +17089,7 @@
       <c r="N49" s="58" t="s">
         <v>382</v>
       </c>
-      <c r="O49" s="240">
+      <c r="O49" s="15">
         <f t="shared" ref="O49:O52" si="16">E49</f>
         <v>0</v>
       </c>
@@ -17197,38 +17111,38 @@
       </c>
     </row>
     <row r="50" spans="1:22" x14ac:dyDescent="0.2">
-      <c r="A50" s="268" t="s">
+      <c r="A50" s="231" t="s">
         <v>56</v>
       </c>
-      <c r="B50" s="269" t="s">
+      <c r="B50" s="232" t="s">
         <v>329</v>
       </c>
-      <c r="C50" s="270">
+      <c r="C50" s="233">
         <v>3</v>
       </c>
-      <c r="D50" s="271">
-        <v>0</v>
-      </c>
-      <c r="E50" s="272">
-        <v>0</v>
-      </c>
-      <c r="F50" s="271">
-        <v>0</v>
-      </c>
-      <c r="G50" s="273" t="s">
+      <c r="D50" s="234">
+        <v>0</v>
+      </c>
+      <c r="E50" s="235">
+        <v>0</v>
+      </c>
+      <c r="F50" s="234">
+        <v>0</v>
+      </c>
+      <c r="G50" s="236" t="s">
         <v>383</v>
       </c>
-      <c r="H50" s="274">
+      <c r="H50" s="237">
         <v>1.53</v>
       </c>
-      <c r="I50" s="274">
+      <c r="I50" s="237">
         <v>1.55</v>
       </c>
-      <c r="J50" s="275">
+      <c r="J50" s="238">
         <f t="shared" si="15"/>
         <v>2.0000000000000018E-2</v>
       </c>
-      <c r="K50" s="300" t="s">
+      <c r="K50" s="258" t="s">
         <v>379</v>
       </c>
       <c r="M50" s="57" t="s">
@@ -17237,7 +17151,7 @@
       <c r="N50" s="58" t="s">
         <v>380</v>
       </c>
-      <c r="O50" s="240">
+      <c r="O50" s="15">
         <f t="shared" si="16"/>
         <v>0</v>
       </c>
@@ -17259,13 +17173,13 @@
       </c>
     </row>
     <row r="51" spans="1:22" x14ac:dyDescent="0.2">
-      <c r="A51" s="276" t="s">
+      <c r="A51" s="239" t="s">
         <v>57</v>
       </c>
       <c r="B51" s="19" t="s">
         <v>343</v>
       </c>
-      <c r="C51" s="277">
+      <c r="C51" s="240">
         <v>4</v>
       </c>
       <c r="D51" s="17">
@@ -17280,17 +17194,17 @@
       <c r="G51" s="44" t="s">
         <v>383</v>
       </c>
-      <c r="H51" s="278">
+      <c r="H51" s="241">
         <v>5.7</v>
       </c>
-      <c r="I51" s="278">
+      <c r="I51" s="241">
         <v>5.69</v>
       </c>
-      <c r="J51" s="279">
+      <c r="J51" s="242">
         <f t="shared" si="15"/>
         <v>-9.9999999999997868E-3</v>
       </c>
-      <c r="K51" s="293" t="s">
+      <c r="K51" s="252" t="s">
         <v>381</v>
       </c>
       <c r="M51" s="57" t="s">
@@ -17299,7 +17213,7 @@
       <c r="N51" s="58" t="s">
         <v>382</v>
       </c>
-      <c r="O51" s="240">
+      <c r="O51" s="15">
         <f t="shared" si="16"/>
         <v>0</v>
       </c>
@@ -17321,13 +17235,13 @@
       </c>
     </row>
     <row r="52" spans="1:22" x14ac:dyDescent="0.2">
-      <c r="A52" s="232" t="s">
+      <c r="A52" s="210" t="s">
         <v>58</v>
       </c>
       <c r="B52" s="22" t="s">
         <v>343</v>
       </c>
-      <c r="C52" s="233">
+      <c r="C52" s="211">
         <v>4</v>
       </c>
       <c r="D52" s="20">
@@ -17342,17 +17256,17 @@
       <c r="G52" s="45" t="s">
         <v>383</v>
       </c>
-      <c r="H52" s="234">
+      <c r="H52" s="212">
         <v>0.01</v>
       </c>
-      <c r="I52" s="234">
+      <c r="I52" s="212">
         <v>-0.02</v>
       </c>
-      <c r="J52" s="235">
+      <c r="J52" s="213">
         <f>I52-H52</f>
         <v>-0.03</v>
       </c>
-      <c r="K52" s="292" t="s">
+      <c r="K52" s="251" t="s">
         <v>381</v>
       </c>
       <c r="M52" s="57" t="s">
@@ -17361,7 +17275,7 @@
       <c r="N52" s="58" t="s">
         <v>382</v>
       </c>
-      <c r="O52" s="240">
+      <c r="O52" s="15">
         <f t="shared" si="16"/>
         <v>0</v>
       </c>
@@ -17414,7 +17328,7 @@
         <f>I53-H53</f>
         <v>0.87000000000000011</v>
       </c>
-      <c r="K53" s="245" t="s">
+      <c r="K53" s="56" t="s">
         <v>381</v>
       </c>
       <c r="M53" s="57" t="s">
